--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486997_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486997_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9659</v>
+        <v>2.7792</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6859</v>
+        <v>2.1841</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2799</v>
+        <v>0.5951</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6373</v>
+        <v>2.7158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.7981</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>1.9177</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7209</v>
+        <v>3.3306</v>
       </c>
       <c r="K2" t="n">
-        <v>1.642</v>
+        <v>2.4366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0789</v>
+        <v>0.8939</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.6147</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8047</v>
+        <v>-1.6385</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7211</v>
+        <v>1.0238</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R2" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9179</v>
+        <v>-0.526</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1704</v>
+        <v>-0.5038</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7475000000000001</v>
+        <v>-0.0222</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9688</v>
+        <v>2.5623</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6998</v>
+        <v>1.6085</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2691</v>
+        <v>0.9539</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7158</v>
+        <v>1.6373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7981</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9177</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3306</v>
+        <v>1.7209</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4366</v>
+        <v>1.642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8939</v>
+        <v>0.0789</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6147</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6385</v>
+        <v>-0.8047</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0238</v>
+        <v>0.7211</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3363</v>
+        <v>0.5144</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9881</v>
+        <v>0.0929</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3482</v>
+        <v>0.4215</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3615</v>
+        <v>0.4257</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1775</v>
+        <v>0.0341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1841</v>
+        <v>0.3916</v>
       </c>
       <c r="G4" t="n">
         <v>0.3318</v>
@@ -766,13 +766,13 @@
         <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5863</v>
+        <v>-0.5221</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.159</v>
+        <v>-0.3023</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4273</v>
+        <v>-0.2198</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1945</v>
+        <v>-0.7107</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3774</v>
+        <v>0.5019</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1829</v>
+        <v>-1.2126</v>
       </c>
       <c r="G5" t="n">
         <v>0.4786</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4141</v>
+        <v>-0.4911</v>
       </c>
       <c r="T5" t="n">
-        <v>1.104</v>
+        <v>0.2284</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6899</v>
+        <v>-0.7195</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6982</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0132</v>
+        <v>-0.9439</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2108</v>
+        <v>0.2735</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8024</v>
+        <v>-1.2174</v>
       </c>
       <c r="G6" t="n">
         <v>0.9732</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5942</v>
+        <v>-0.5249</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1198</v>
+        <v>-0.6355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5256</v>
+        <v>0.1106</v>
       </c>
       <c r="V6" t="n">
         <v>-2.0082</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8079</v>
+        <v>-1.1531</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1226</v>
+        <v>-0.4678</v>
       </c>
       <c r="F7" t="n">
         <v>-0.6853</v>
@@ -1000,10 +1000,10 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0344</v>
+        <v>-0.3797</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9222</v>
+        <v>-0.2674</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1122</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0785</v>
+        <v>-1.9861</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7149</v>
+        <v>-3.2404</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3636</v>
+        <v>1.2543</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2312</v>
+        <v>-0.6165</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2653</v>
+        <v>-2.0242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0341</v>
+        <v>1.4077</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7268</v>
+        <v>-0.9466</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.016</v>
+        <v>-1.4463</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7108</v>
+        <v>0.4997</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5044</v>
+        <v>0.3301</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2492</v>
+        <v>-0.578</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7449</v>
+        <v>0.9081</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9829</v>
+        <v>-0.9938</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9881</v>
+        <v>-0.4806</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0052</v>
+        <v>-0.5132</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4805</v>
+        <v>0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1262</v>
+        <v>-2.0109</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.558</v>
+        <v>-1.4398</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5683</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1927</v>
+        <v>-1.2312</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9271</v>
+        <v>-1.2653</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2655</v>
+        <v>0.0341</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0966</v>
+        <v>-0.7268</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5966</v>
+        <v>-0.016</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5</v>
+        <v>-0.7108</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.096</v>
+        <v>-0.5044</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3305</v>
+        <v>-1.2492</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2345</v>
+        <v>0.7449</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9967</v>
+        <v>-0.9153</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1034</v>
+        <v>-0.713</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1068</v>
+        <v>-0.2023</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2875</v>
+        <v>-0.4805</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0082</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1325</v>
+        <v>-2.5032</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.209</v>
+        <v>-2.3901</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0765</v>
+        <v>-0.1132</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6165</v>
+        <v>-3.5484</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0242</v>
+        <v>-1.5406</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4077</v>
+        <v>-2.0078</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9466</v>
+        <v>-3.4601</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4463</v>
+        <v>-0.6837</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4997</v>
+        <v>-2.7764</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3301</v>
+        <v>-0.0883</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.578</v>
+        <v>-0.8569</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9081</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1402</v>
+        <v>-0.6325</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4492</v>
+        <v>-0.3489</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.2836</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.62</v>
+        <v>-4.7587</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3586</v>
+        <v>-3.3091</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2614</v>
+        <v>-1.4497</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5484</v>
+        <v>-2.1927</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5406</v>
+        <v>-1.9271</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0078</v>
+        <v>-0.2655</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4601</v>
+        <v>-1.0966</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6837</v>
+        <v>-0.5966</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7764</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0883</v>
+        <v>-1.096</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8569</v>
+        <v>-1.3305</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.2345</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4374</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7493</v>
+        <v>0.3641</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3174</v>
+        <v>0.3523</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4318</v>
+        <v>0.0118</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2402</v>
+        <v>-1.2875</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4189</v>
+        <v>0.7207</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1786</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="12">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.287600000000001</v>
+        <v>-8.2994</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2333</v>
+        <v>-6.245100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0543</v>
+        <v>-2.0544</v>
       </c>
       <c r="G12" t="n">
         <v>-2.011999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.234400000000001</v>
+        <v>-7.2344</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2224</v>
+        <v>5.222399999999999</v>
       </c>
       <c r="J12" t="n">
         <v>1.096899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.047</v>
+        <v>2.046999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9501000000000002</v>
+        <v>-0.9501000000000004</v>
       </c>
       <c r="M12" t="n">
         <v>-3.1087</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.2814</v>
+        <v>-9.281400000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>6.172700000000001</v>
+        <v>6.1727</v>
       </c>
       <c r="P12" t="n">
         <v>2.0534</v>
@@ -1390,10 +1390,10 @@
         <v>10.2671</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0949</v>
+        <v>-4.1069</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.566</v>
+        <v>-2.5779</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5289</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.701</v>
+        <v>5.1368</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0048</v>
+        <v>4.737</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6962</v>
+        <v>0.3997</v>
       </c>
       <c r="G13" t="n">
         <v>0.6845</v>
@@ -1468,13 +1468,13 @@
         <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4457</v>
+        <v>0.8814</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9804</v>
+        <v>-0.2481</v>
       </c>
       <c r="U13" t="n">
-        <v>1.426</v>
+        <v>1.1296</v>
       </c>
       <c r="V13" t="n">
         <v>3.7761</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4706</v>
+        <v>4.0382</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9031</v>
+        <v>1.5893</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5675</v>
+        <v>2.4489</v>
       </c>
       <c r="G14" t="n">
         <v>2.7286</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1957</v>
+        <v>0.7633</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5384</v>
+        <v>0.2246</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6573</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4805</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0573</v>
+        <v>2.9969</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1261</v>
+        <v>0.7432</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9312</v>
+        <v>2.2537</v>
       </c>
       <c r="G15" t="n">
-        <v>0.861</v>
+        <v>0.3738</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7239</v>
+        <v>-1.3233</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1372</v>
+        <v>1.697</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0982</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2554</v>
+        <v>-1.1898</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1579</v>
+        <v>1.0916</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9586</v>
+        <v>0.4719</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9792999999999999</v>
+        <v>-0.1335</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0207</v>
+        <v>0.6054</v>
       </c>
       <c r="P15" t="n">
         <v>-0.2053</v>
@@ -1624,28 +1624,28 @@
         <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9211</v>
+        <v>1.3008</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7699</v>
+        <v>0.6894</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1513</v>
+        <v>0.6113</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4805</v>
+        <v>1.5277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7762</v>
+        <v>2.6801</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7892</v>
+        <v>0.4524</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9869</v>
+        <v>2.2276</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3738</v>
+        <v>0.861</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3233</v>
+        <v>0.7239</v>
       </c>
       <c r="I16" t="n">
-        <v>1.697</v>
+        <v>0.1372</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0982</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1898</v>
+        <v>-0.2554</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0916</v>
+        <v>0.1579</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4719</v>
+        <v>0.9586</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1335</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6054</v>
+        <v>-0.0207</v>
       </c>
       <c r="P16" t="n">
         <v>-0.2053</v>
@@ -1702,22 +1702,22 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>1.5439</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7355</v>
+        <v>1.0962</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3446</v>
+        <v>0.4477</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5277</v>
+        <v>0.4805</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0803</v>
+        <v>0.3538</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2686</v>
+        <v>0.2544</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1883</v>
+        <v>0.0994</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0163</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1229</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2907</v>
+        <v>0.2323</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4136</v>
+        <v>0.3247</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4189</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1054</v>
+        <v>0.0599</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2395</v>
+        <v>-0.5431</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1341</v>
+        <v>0.603</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1813</v>
+        <v>1.4042</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9311</v>
+        <v>3.2407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2502</v>
+        <v>-1.8365</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7753</v>
+        <v>2.3163</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7359</v>
+        <v>3.7374</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>-1.4211</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.594</v>
+        <v>-0.9121</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8047</v>
+        <v>-0.4967</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2107</v>
+        <v>-0.4154</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1856</v>
+        <v>0.434</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0386</v>
+        <v>-0.2597</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1469</v>
+        <v>0.6937</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>0.4805</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3445</v>
+        <v>-0.2396</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0661</v>
+        <v>-0.3441</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7216</v>
+        <v>0.1044</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4042</v>
+        <v>1.1813</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2407</v>
+        <v>0.9311</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8365</v>
+        <v>0.2502</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3163</v>
+        <v>1.7753</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7374</v>
+        <v>1.7359</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4211</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9121</v>
+        <v>-0.594</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4967</v>
+        <v>-0.8047</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4154</v>
+        <v>0.2107</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0295</v>
+        <v>0.0513</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7827</v>
+        <v>-0.066</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8123</v>
+        <v>0.1173</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4805</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9376</v>
+        <v>-0.3172</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6974</v>
+        <v>-1.1042</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2402</v>
+        <v>0.787</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6974</v>
+        <v>-2.1696</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.3145</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6974</v>
+        <v>-2.484</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6974</v>
+        <v>-2.3756</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.1912</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6974</v>
+        <v>-2.1844</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.2061</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.5057</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.2996</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2363</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1435</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2586</v>
+        <v>-0.833</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0456</v>
+        <v>-0.5927</v>
       </c>
       <c r="F21" t="n">
-        <v>0.787</v>
+        <v>-0.2402</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1696</v>
+        <v>-0.6974</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3145</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.484</v>
+        <v>-0.6974</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3756</v>
+        <v>-0.6974</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1912</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1844</v>
+        <v>-0.6974</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2061</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5057</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2996</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8486</v>
+        <v>0.1046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1435</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5658</v>
+        <v>-1.5362</v>
       </c>
       <c r="E22" t="n">
         <v>-0.9019</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6639</v>
+        <v>-0.6343</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1749</v>
@@ -2170,13 +2170,13 @@
         <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.5666</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3328</v>
+        <v>-0.3031</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4253</v>
+        <v>-3.0522</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5498</v>
+        <v>-2.236</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.8162</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1634</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.2111</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3875</v>
+        <v>-0.0737</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1967</v>
+        <v>-0.1374</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.287599999999999</v>
+        <v>9.287500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0543</v>
+        <v>2.054299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>7.233200000000001</v>
+        <v>7.233000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0118</v>
+        <v>2.011799999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>7.234400000000001</v>
+        <v>7.2344</v>
       </c>
       <c r="I24" t="n">
         <v>-5.2225</v>
       </c>
       <c r="J24" t="n">
-        <v>3.108700000000001</v>
+        <v>3.1087</v>
       </c>
       <c r="K24" t="n">
-        <v>9.281599999999999</v>
+        <v>9.281600000000001</v>
       </c>
       <c r="L24" t="n">
         <v>-6.1726</v>
@@ -2326,16 +2326,16 @@
         <v>8.213800000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>5.0949</v>
+        <v>5.094899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.529</v>
+        <v>1.5289</v>
       </c>
       <c r="U24" t="n">
-        <v>3.566000000000001</v>
+        <v>3.5661</v>
       </c>
       <c r="V24" t="n">
-        <v>4.2341</v>
+        <v>4.234100000000001</v>
       </c>
       <c r="W24" t="n">
         <v>7.6836</v>
